--- a/data/trans_camb/P57_AC_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P57_AC_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 4,98</t>
+          <t>-7,67; 5,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,67; 22,06</t>
+          <t>9,76; 22,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,92; -5,81</t>
+          <t>-24,75; -5,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 7,43</t>
+          <t>-5,37; 7,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,51; 19,86</t>
+          <t>7,57; 19,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,01; -7,72</t>
+          <t>-25,16; -7,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 4,66</t>
+          <t>-4,9; 4,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,61; 19,43</t>
+          <t>10,48; 19,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-22,56; -8,58</t>
+          <t>-22,38; -9,26</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 9,06</t>
+          <t>-12,39; 9,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,62; 40,22</t>
+          <t>15,57; 39,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,11; -10,36</t>
+          <t>-41,75; -9,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 13,0</t>
+          <t>-8,35; 12,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,16; 35,06</t>
+          <t>11,83; 34,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,89; -13,03</t>
+          <t>-40,22; -12,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 7,98</t>
+          <t>-7,93; 6,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 33,67</t>
+          <t>17,17; 34,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-36,74; -14,79</t>
+          <t>-36,86; -15,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 4,6</t>
+          <t>-5,48; 5,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,81; 19,08</t>
+          <t>8,95; 19,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 3,04</t>
+          <t>-11,65; 2,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 8,62</t>
+          <t>-1,93; 8,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 17,3</t>
+          <t>7,39; 17,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,89; -9,08</t>
+          <t>-38,3; -9,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 5,37</t>
+          <t>-2,33; 5,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,12; 16,94</t>
+          <t>9,55; 16,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-25,84; -5,76</t>
+          <t>-23,56; -5,87</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 7,61</t>
+          <t>-8,26; 8,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,38; 31,95</t>
+          <t>13,67; 31,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 4,98</t>
+          <t>-18,13; 3,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 13,48</t>
+          <t>-2,79; 14,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,07; 27,11</t>
+          <t>10,71; 27,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,89; -13,86</t>
+          <t>-55,93; -14,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 8,57</t>
+          <t>-3,47; 8,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,85; 26,94</t>
+          <t>14,48; 27,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,1; -9,15</t>
+          <t>-35,93; -9,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 4,78</t>
+          <t>-5,74; 5,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 14,0</t>
+          <t>4,15; 14,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,98; -2,33</t>
+          <t>-13,71; -2,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 9,37</t>
+          <t>-0,31; 9,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 14,28</t>
+          <t>4,93; 14,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,98; -5,29</t>
+          <t>-14,65; -5,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 6,03</t>
+          <t>-1,79; 5,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 12,94</t>
+          <t>5,81; 12,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,16; -5,22</t>
+          <t>-12,82; -5,24</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 7,28</t>
+          <t>-8,06; 7,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,11; 21,37</t>
+          <t>5,8; 21,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,68; -3,59</t>
+          <t>-19,27; -3,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 14,1</t>
+          <t>-0,43; 13,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,9; 21,04</t>
+          <t>6,88; 21,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,83; -7,82</t>
+          <t>-20,29; -7,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 8,97</t>
+          <t>-2,51; 8,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,7; 19,2</t>
+          <t>8,19; 18,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-18,5; -7,89</t>
+          <t>-18,02; -7,81</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 3,51</t>
+          <t>-8,19; 3,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,99; 15,45</t>
+          <t>4,49; 15,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-52,34; -7,61</t>
+          <t>-52,24; -7,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,69; 13,78</t>
+          <t>2,91; 14,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,13; 18,9</t>
+          <t>8,92; 18,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,34; -3,52</t>
+          <t>-19,04; -2,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 7,04</t>
+          <t>-0,5; 7,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,15; 15,48</t>
+          <t>8,31; 15,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-39,28; -7,7</t>
+          <t>-38,49; -7,7</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 5,15</t>
+          <t>-10,95; 4,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,88; 22,83</t>
+          <t>6,13; 23,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-71,57; -11,02</t>
+          <t>-71,02; -10,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,1; 20,38</t>
+          <t>3,88; 20,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,46; 28,9</t>
+          <t>12,17; 28,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,07; -5,29</t>
+          <t>-26,85; -4,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 10,34</t>
+          <t>-0,66; 10,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,19; 22,8</t>
+          <t>11,24; 22,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-55,67; -10,88</t>
+          <t>-53,88; -11,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 0,26</t>
+          <t>-13,09; 0,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,9; 16,57</t>
+          <t>4,87; 17,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 3,41</t>
+          <t>-9,6; 3,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 2,99</t>
+          <t>-9,52; 3,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,91; 12,67</t>
+          <t>1,85; 12,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 0,25</t>
+          <t>-10,34; -0,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,55; -0,54</t>
+          <t>-8,97; -0,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,9; 12,94</t>
+          <t>5,03; 13,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -0,05</t>
+          <t>-7,55; -0,11</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 0,31</t>
+          <t>-17,93; 1,27</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,52; 24,72</t>
+          <t>6,56; 25,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 5,15</t>
+          <t>-12,85; 4,92</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 4,17</t>
+          <t>-11,84; 4,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,55; 17,28</t>
+          <t>2,27; 16,75</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 0,37</t>
+          <t>-12,91; -0,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,32; -0,78</t>
+          <t>-11,87; -0,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6,41; 18,34</t>
+          <t>6,67; 18,63</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-10,14; -0,07</t>
+          <t>-9,88; -0,06</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 3,55</t>
+          <t>-10,5; 3,92</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 7,77</t>
+          <t>-5,72; 7,09</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,65; -4,08</t>
+          <t>-17,37; -5,01</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 5,22</t>
+          <t>-7,13; 5,05</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,56; 16,17</t>
+          <t>5,76; 15,8</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-17,25; -6,29</t>
+          <t>-16,98; -6,32</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 1,98</t>
+          <t>-7,07; 2,6</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,14; 10,77</t>
+          <t>1,82; 10,36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-15,62; -7,88</t>
+          <t>-15,61; -7,4</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 4,77</t>
+          <t>-13,01; 5,42</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 10,58</t>
+          <t>-7,17; 9,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-20,59; -5,88</t>
+          <t>-21,52; -6,93</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 7,04</t>
+          <t>-8,87; 6,78</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,19; 21,98</t>
+          <t>7,32; 21,8</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-21,38; -8,5</t>
+          <t>-21,2; -8,61</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 2,62</t>
+          <t>-8,93; 3,51</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2,61; 14,24</t>
+          <t>2,32; 13,84</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-19,44; -10,39</t>
+          <t>-19,67; -9,92</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 4,65</t>
+          <t>-11,82; 3,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 12,5</t>
+          <t>-2,1; 11,9</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,6; -1,44</t>
+          <t>-15,62; -1,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 1,83</t>
+          <t>-10,55; 2,4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,03; 11,57</t>
+          <t>0,25; 11,91</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-12,09; -1,96</t>
+          <t>-11,97; -0,58</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 0,42</t>
+          <t>-9,17; 0,68</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,22</t>
+          <t>1,05; 10,09</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,8; -3,21</t>
+          <t>-12,01; -3,41</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 5,96</t>
+          <t>-14,23; 5,06</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 16,58</t>
+          <t>-2,53; 15,73</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,47; -1,94</t>
+          <t>-18,73; -1,38</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 2,32</t>
+          <t>-12,48; 3,07</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,1; 15,0</t>
+          <t>0,29; 15,36</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-14,28; -2,51</t>
+          <t>-14,28; -0,94</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 0,55</t>
+          <t>-11,06; 0,92</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>1,23; 12,93</t>
+          <t>1,25; 13,09</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-14,1; -4,06</t>
+          <t>-14,27; -4,33</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 0,73</t>
+          <t>-3,91; 0,67</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>8,83; 13,18</t>
+          <t>8,92; 13,3</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-24,46; -5,9</t>
+          <t>-23,79; -6,01</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,83</t>
+          <t>0,41; 4,69</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>9,4; 13,2</t>
+          <t>9,29; 13,31</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-14,34; -6,99</t>
+          <t>-14,02; -6,94</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,12</t>
+          <t>-1,04; 2,19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>9,61; 12,85</t>
+          <t>9,66; 12,61</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-17,94; -7,58</t>
+          <t>-17,66; -7,33</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 1,05</t>
+          <t>-5,69; 0,99</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>12,78; 19,81</t>
+          <t>12,94; 19,95</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-36,54; -8,82</t>
+          <t>-34,79; -8,88</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,94</t>
+          <t>0,57; 6,72</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>13,07; 18,98</t>
+          <t>12,84; 19,17</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-20,4; -10,11</t>
+          <t>-20,05; -9,99</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,1</t>
+          <t>-1,49; 3,2</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>13,69; 18,79</t>
+          <t>13,78; 18,44</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-26,11; -10,98</t>
+          <t>-25,31; -10,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_AC_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P57_AC_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-15,42</t>
+          <t>-13,19</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-16,47</t>
+          <t>-13,39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-15,99</t>
+          <t>-13,32</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 5,19</t>
+          <t>-7,72; 4,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,76; 22,33</t>
+          <t>10,15; 22,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,75; -5,42</t>
+          <t>-22,61; -3,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 7,23</t>
+          <t>-5,41; 6,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 19,78</t>
+          <t>7,2; 19,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,16; -7,77</t>
+          <t>-22,1; -5,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 4,0</t>
+          <t>-4,82; 3,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,48; 19,37</t>
+          <t>10,83; 18,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-22,38; -9,26</t>
+          <t>-20,04; -7,44</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-26,21%</t>
+          <t>-22,41%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-26,97%</t>
+          <t>-21,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-26,69%</t>
+          <t>-22,23%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 9,25</t>
+          <t>-12,63; 8,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,57; 39,86</t>
+          <t>16,43; 39,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,75; -9,6</t>
+          <t>-37,76; -6,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 12,58</t>
+          <t>-8,51; 11,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,83; 34,56</t>
+          <t>10,96; 33,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,22; -12,83</t>
+          <t>-34,94; -8,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 6,93</t>
+          <t>-7,87; 6,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,17; 34,2</t>
+          <t>17,43; 32,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-36,86; -15,69</t>
+          <t>-32,34; -12,63</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-4,16</t>
+          <t>-2,6</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-19,05</t>
+          <t>-9,88</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-12,04</t>
+          <t>-6,16</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 5,37</t>
+          <t>-5,73; 4,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,95; 19,1</t>
+          <t>9,09; 18,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 2,28</t>
+          <t>-10,05; 4,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 8,9</t>
+          <t>-2,15; 8,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 17,62</t>
+          <t>7,08; 17,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,3; -9,62</t>
+          <t>-15,98; -4,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 5,22</t>
+          <t>-2,17; 5,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,55; 16,86</t>
+          <t>9,6; 16,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-23,56; -5,87</t>
+          <t>-10,74; -0,97</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-6,59%</t>
+          <t>-4,12%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-28,84%</t>
+          <t>-14,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-18,67%</t>
+          <t>-9,56%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 8,81</t>
+          <t>-8,84; 7,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,67; 31,8</t>
+          <t>13,8; 31,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,13; 3,73</t>
+          <t>-15,39; 6,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 14,11</t>
+          <t>-3,3; 13,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,71; 27,84</t>
+          <t>10,25; 27,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,93; -14,5</t>
+          <t>-23,37; -6,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 8,33</t>
+          <t>-3,28; 8,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,48; 27,38</t>
+          <t>14,51; 26,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,93; -9,3</t>
+          <t>-16,42; -1,62</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-8,23</t>
+          <t>-6,23</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-10,13</t>
+          <t>-8,28</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-9,2</t>
+          <t>-7,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 5,13</t>
+          <t>-5,92; 5,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,15; 14,08</t>
+          <t>4,41; 14,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -2,22</t>
+          <t>-11,26; 0,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 9,22</t>
+          <t>-0,05; 10,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,93; 14,29</t>
+          <t>4,98; 14,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -5,19</t>
+          <t>-13,39; -3,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 5,74</t>
+          <t>-0,97; 5,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 12,6</t>
+          <t>5,97; 12,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,82; -5,24</t>
+          <t>-11,25; -3,41</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-11,95%</t>
+          <t>-9,05%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-14,46%</t>
+          <t>-11,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-13,25%</t>
+          <t>-10,48%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 7,82</t>
+          <t>-8,13; 7,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,8; 21,44</t>
+          <t>6,15; 22,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,27; -3,39</t>
+          <t>-15,76; 0,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 13,66</t>
+          <t>-0,19; 15,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,88; 21,13</t>
+          <t>6,99; 21,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,29; -7,59</t>
+          <t>-18,6; -5,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 8,57</t>
+          <t>-1,37; 8,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,19; 18,7</t>
+          <t>8,37; 18,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-18,02; -7,81</t>
+          <t>-15,79; -5,19</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-26,78</t>
+          <t>-9,08</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,95</t>
+          <t>-5,46</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-18,8</t>
+          <t>-7,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 3,06</t>
+          <t>-7,9; 3,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 15,88</t>
+          <t>4,73; 15,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-52,24; -7,36</t>
+          <t>-14,95; -3,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,91; 14,06</t>
+          <t>3,15; 14,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,92; 18,67</t>
+          <t>8,74; 18,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,04; -2,92</t>
+          <t>-10,32; -0,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 7,28</t>
+          <t>-0,97; 6,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,31; 15,37</t>
+          <t>8,24; 15,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-38,49; -7,7</t>
+          <t>-10,96; -3,26</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-37,73%</t>
+          <t>-12,8%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-12,81%</t>
+          <t>-7,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-26,7%</t>
+          <t>-10,29%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 4,54</t>
+          <t>-10,65; 5,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,13; 23,89</t>
+          <t>6,35; 22,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-71,02; -10,52</t>
+          <t>-20,12; -5,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,88; 20,96</t>
+          <t>4,48; 21,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,17; 28,34</t>
+          <t>12,04; 29,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,85; -4,56</t>
+          <t>-14,14; -0,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 10,67</t>
+          <t>-1,27; 10,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,24; 22,46</t>
+          <t>11,39; 23,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,88; -11,01</t>
+          <t>-15,22; -4,8</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,49</t>
+          <t>-1,82</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,31</t>
+          <t>-4,84</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,99</t>
+          <t>-3,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 0,85</t>
+          <t>-13,41; 0,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,87; 17,22</t>
+          <t>5,1; 16,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 3,29</t>
+          <t>-7,18; 4,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 3,13</t>
+          <t>-9,18; 2,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,85; 12,33</t>
+          <t>2,19; 12,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,34; -0,32</t>
+          <t>-9,89; -0,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,97; -0,36</t>
+          <t>-9,45; -0,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,03; 13,2</t>
+          <t>4,87; 12,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,55; -0,11</t>
+          <t>-7,3; 0,32</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-3,53%</t>
+          <t>-2,59%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-6,93%</t>
+          <t>-6,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-5,43%</t>
+          <t>-4,63%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 1,27</t>
+          <t>-18,08; 0,57</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,56; 25,93</t>
+          <t>6,88; 25,02</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 4,92</t>
+          <t>-9,75; 6,52</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 4,2</t>
+          <t>-11,52; 4,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,27; 16,75</t>
+          <t>2,76; 17,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,91; -0,34</t>
+          <t>-12,42; -0,01</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-11,87; -0,46</t>
+          <t>-12,55; -0,69</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6,67; 18,63</t>
+          <t>6,47; 18,13</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,88; -0,06</t>
+          <t>-9,44; 0,44</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-10,98</t>
+          <t>-10,8</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-12,05</t>
+          <t>-11,64</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-11,54</t>
+          <t>-11,24</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 3,92</t>
+          <t>-10,25; 3,78</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 7,09</t>
+          <t>-5,64; 7,86</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-17,37; -5,01</t>
+          <t>-17,19; -4,79</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 5,05</t>
+          <t>-6,92; 5,1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,76; 15,8</t>
+          <t>6,23; 16,61</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,98; -6,32</t>
+          <t>-16,69; -6,22</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 2,6</t>
+          <t>-6,93; 2,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,82; 10,36</t>
+          <t>2,03; 10,43</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-15,61; -7,4</t>
+          <t>-15,13; -6,92</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-14,21%</t>
+          <t>-13,98%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-15,51%</t>
+          <t>-15,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-14,9%</t>
+          <t>-14,51%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 5,42</t>
+          <t>-12,67; 5,22</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 9,6</t>
+          <t>-6,97; 10,58</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-21,52; -6,93</t>
+          <t>-21,54; -6,59</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 6,78</t>
+          <t>-8,53; 6,9</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,32; 21,8</t>
+          <t>7,71; 22,44</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-21,2; -8,61</t>
+          <t>-20,7; -8,19</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 3,51</t>
+          <t>-8,72; 2,96</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2,32; 13,84</t>
+          <t>2,47; 13,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-19,67; -9,92</t>
+          <t>-19,03; -9,44</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-8,27</t>
+          <t>-8,04</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-7,04</t>
+          <t>-7,09</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-7,56</t>
+          <t>-7,5</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 3,87</t>
+          <t>-11,5; 3,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 11,9</t>
+          <t>-1,3; 12,24</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,62; -1,12</t>
+          <t>-14,98; -0,41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 2,4</t>
+          <t>-10,63; 1,72</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,25; 11,91</t>
+          <t>-0,34; 11,62</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-11,97; -0,58</t>
+          <t>-12,31; -1,67</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 0,68</t>
+          <t>-8,99; 0,6</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,05; 10,09</t>
+          <t>1,02; 10,21</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-12,01; -3,41</t>
+          <t>-11,95; -3,17</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-10,44%</t>
+          <t>-10,14%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-8,64%</t>
+          <t>-8,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-9,37%</t>
+          <t>-9,3%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 5,06</t>
+          <t>-13,88; 4,97</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 15,73</t>
+          <t>-1,59; 16,49</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,73; -1,38</t>
+          <t>-18,09; -0,6</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 3,07</t>
+          <t>-12,63; 2,13</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,29; 15,36</t>
+          <t>-0,45; 15,01</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-14,28; -0,94</t>
+          <t>-14,43; -2,16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 0,92</t>
+          <t>-10,94; 0,72</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>1,25; 13,09</t>
+          <t>1,21; 13,18</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-14,27; -4,33</t>
+          <t>-14,24; -4,04</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-11,15</t>
+          <t>-5,53</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-9,66</t>
+          <t>-6,86</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-10,43</t>
+          <t>-6,2</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,67</t>
+          <t>-3,83; 0,86</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>8,92; 13,3</t>
+          <t>9,16; 13,3</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-23,79; -6,01</t>
+          <t>-7,98; -3,01</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,69</t>
+          <t>0,29; 4,84</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,31</t>
+          <t>9,25; 13,3</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-14,02; -6,94</t>
+          <t>-9,14; -4,89</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,19</t>
+          <t>-1,09; 2,15</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>9,66; 12,61</t>
+          <t>9,83; 12,8</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-17,66; -7,33</t>
+          <t>-7,84; -4,43</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-16,4%</t>
+          <t>-8,14%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-13,66%</t>
+          <t>-9,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-15,04%</t>
+          <t>-8,94%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 0,99</t>
+          <t>-5,53; 1,31</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>12,94; 19,95</t>
+          <t>13,23; 20,02</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-34,79; -8,88</t>
+          <t>-11,57; -4,58</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,72</t>
+          <t>0,43; 6,98</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>12,84; 19,17</t>
+          <t>12,77; 19,14</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-20,05; -9,99</t>
+          <t>-12,69; -7,03</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,2</t>
+          <t>-1,55; 3,13</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>13,78; 18,44</t>
+          <t>14,05; 18,72</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-25,31; -10,62</t>
+          <t>-11,19; -6,47</t>
         </is>
       </c>
     </row>
